--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T10:55:45+00:00</t>
+    <t>2023-04-05T15:18:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:18:36+00:00</t>
+    <t>2023-04-05T15:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:41:27+00:00</t>
+    <t>2023-04-05T15:52:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:52:08+00:00</t>
+    <t>2023-04-05T15:53:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:53:16+00:00</t>
+    <t>2023-04-05T15:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:55:13+00:00</t>
+    <t>2023-04-05T16:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:00:25+00:00</t>
+    <t>2023-04-05T16:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3241" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="386">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:20:25+00:00</t>
+    <t>2023-04-05T16:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -762,162 +762,6 @@
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
   </si>
   <si>
-    <t>HealthcareService.type.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R280-DisciplineEquipementSocial/FHIR/TRE-R280-DisciplineEquipementSocial</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>HealthcareService.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
     <t>HealthcareService.specialty</t>
   </si>
   <si>
@@ -964,6 +808,9 @@
     <t>Further description of the service as it would be presented to a consumer while searching.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>.name</t>
   </si>
   <si>
@@ -1131,42 +978,6 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J137-Clientele-RASS/FHIR/JDV-J137-Clientele-RASS</t>
   </si>
   <si>
-    <t>HealthcareService.eligibility.code.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.eligibility.code.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.eligibility.code.coding</t>
-  </si>
-  <si>
-    <t>HealthcareService.eligibility.code.coding.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.eligibility.code.coding.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.eligibility.code.coding.system</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R279-Clientele/FHIR/TRE-R279-Clientele</t>
-  </si>
-  <si>
-    <t>HealthcareService.eligibility.code.coding.version</t>
-  </si>
-  <si>
-    <t>HealthcareService.eligibility.code.coding.code</t>
-  </si>
-  <si>
-    <t>HealthcareService.eligibility.code.coding.display</t>
-  </si>
-  <si>
-    <t>HealthcareService.eligibility.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t>HealthcareService.eligibility.code.text</t>
-  </si>
-  <si>
     <t>HealthcareService.eligibility.comment</t>
   </si>
   <si>
@@ -1219,42 +1030,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J138-TypeActivite-RASS/FHIR/JDV-J138-TypeActivite-RASS</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.system</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R209-TypeActivite/FHIR/TRE-R209-TypeActivite</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.version</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.code</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.display</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.coding.userSelected</t>
-  </si>
-  <si>
-    <t>HealthcareService.characteristic.text</t>
   </si>
   <si>
     <t>HealthcareService.communication</t>
@@ -1733,11 +1508,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL94"/>
+  <dimension ref="A1:AL61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.99609375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.99609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.1328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="49.1328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.57421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -4495,7 +4270,7 @@
         <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>73</v>
@@ -4504,18 +4279,20 @@
         <v>73</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>98</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>73</v>
@@ -4540,13 +4317,13 @@
         <v>73</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>73</v>
+        <v>242</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>73</v>
+        <v>243</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -4564,22 +4341,22 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>100</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>101</v>
+        <v>238</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>73</v>
@@ -4587,21 +4364,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -4610,19 +4387,19 @@
         <v>73</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>104</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>105</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>107</v>
+        <v>248</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4660,19 +4437,19 @@
         <v>73</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>111</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4684,21 +4461,21 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>112</v>
+        <v>218</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>95</v>
+        <v>249</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>73</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4709,7 +4486,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -4721,20 +4498,18 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>73</v>
       </c>
@@ -4782,13 +4557,13 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>93</v>
@@ -4797,7 +4572,7 @@
         <v>94</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>73</v>
@@ -4805,10 +4580,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4819,7 +4594,7 @@
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -4828,18 +4603,20 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>98</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>73</v>
@@ -4888,7 +4665,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>100</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4897,13 +4674,13 @@
         <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>101</v>
+        <v>260</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -4911,21 +4688,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -4937,16 +4714,16 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>104</v>
+        <v>262</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>105</v>
+        <v>263</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>106</v>
+        <v>264</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>107</v>
+        <v>265</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4984,34 +4761,34 @@
         <v>73</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>111</v>
+        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>95</v>
+        <v>266</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
@@ -5019,10 +4796,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5033,7 +4810,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -5045,26 +4822,24 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>125</v>
+        <v>268</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>255</v>
+        <v>73</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>73</v>
@@ -5106,7 +4881,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -5118,10 +4893,10 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>94</v>
+        <v>272</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>73</v>
@@ -5129,10 +4904,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5143,7 +4918,7 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>
@@ -5152,19 +4927,19 @@
         <v>73</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>97</v>
+        <v>275</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5214,22 +4989,22 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>94</v>
+        <v>279</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
@@ -5237,10 +5012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5251,7 +5026,7 @@
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -5260,23 +5035,21 @@
         <v>73</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>160</v>
+        <v>245</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>73</v>
       </c>
@@ -5324,22 +5097,22 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
@@ -5347,10 +5120,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5361,7 +5134,7 @@
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -5370,23 +5143,21 @@
         <v>73</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>73</v>
       </c>
@@ -5410,13 +5181,13 @@
         <v>73</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>73</v>
+        <v>288</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>73</v>
+        <v>290</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>73</v>
@@ -5434,13 +5205,13 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>93</v>
@@ -5449,7 +5220,7 @@
         <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
@@ -5457,10 +5228,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5471,7 +5242,7 @@
         <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>73</v>
@@ -5480,23 +5251,19 @@
         <v>73</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>73</v>
       </c>
@@ -5544,13 +5311,13 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>93</v>
@@ -5559,7 +5326,7 @@
         <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>283</v>
+        <v>101</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
@@ -5567,10 +5334,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5590,23 +5357,19 @@
         <v>73</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>97</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>285</v>
+        <v>98</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>73</v>
       </c>
@@ -5654,7 +5417,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>289</v>
+        <v>100</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5663,13 +5426,13 @@
         <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>290</v>
+        <v>101</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5677,21 +5440,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>73</v>
@@ -5700,19 +5463,19 @@
         <v>73</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>222</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>292</v>
+        <v>105</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>234</v>
+        <v>107</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5738,31 +5501,31 @@
         <v>73</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>294</v>
+        <v>73</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>295</v>
+        <v>73</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>291</v>
+        <v>111</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5774,10 +5537,10 @@
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>238</v>
+        <v>95</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
@@ -5785,44 +5548,46 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>73</v>
+        <v>299</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>297</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>73</v>
       </c>
@@ -5870,7 +5635,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5882,13 +5647,13 @@
         <v>93</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>218</v>
+        <v>112</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>301</v>
+        <v>95</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>302</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
@@ -5907,7 +5672,7 @@
         <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>73</v>
@@ -5916,10 +5681,10 @@
         <v>73</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>304</v>
@@ -5928,7 +5693,7 @@
         <v>305</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5954,13 +5719,13 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>73</v>
+        <v>306</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>73</v>
+        <v>307</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>73</v>
@@ -5993,7 +5758,7 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>73</v>
@@ -6001,10 +5766,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6024,19 +5789,19 @@
         <v>73</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>97</v>
+        <v>262</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6086,7 +5851,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -6101,7 +5866,7 @@
         <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -6109,10 +5874,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6135,7 +5900,7 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>313</v>
+        <v>222</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>314</v>
@@ -6170,13 +5935,13 @@
         <v>73</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>73</v>
+        <v>317</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>73</v>
+        <v>318</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>73</v>
@@ -6194,13 +5959,13 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>93</v>
@@ -6209,7 +5974,7 @@
         <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>73</v>
@@ -6217,10 +5982,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6231,7 +5996,7 @@
         <v>74</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>73</v>
@@ -6240,19 +6005,19 @@
         <v>73</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>319</v>
+        <v>222</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6278,13 +6043,13 @@
         <v>73</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>73</v>
+        <v>324</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>73</v>
+        <v>325</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>73</v>
@@ -6302,22 +6067,22 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>323</v>
+        <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
@@ -6325,10 +6090,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6351,7 +6116,7 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>326</v>
+        <v>222</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>327</v>
@@ -6386,13 +6151,13 @@
         <v>73</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>73</v>
@@ -6410,7 +6175,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -6422,10 +6187,10 @@
         <v>93</v>
       </c>
       <c r="AJ43" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK43" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>73</v>
@@ -6433,10 +6198,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6459,16 +6224,16 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>297</v>
+        <v>222</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>334</v>
-      </c>
       <c r="N44" t="s" s="2">
-        <v>335</v>
+        <v>234</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6494,13 +6259,13 @@
         <v>73</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>73</v>
+        <v>334</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>73</v>
+        <v>335</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>73</v>
@@ -6518,7 +6283,7 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
@@ -6530,10 +6295,10 @@
         <v>93</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>73</v>
@@ -6541,10 +6306,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6567,17 +6332,15 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>340</v>
-      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>73</v>
@@ -6602,13 +6365,13 @@
         <v>73</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>339</v>
+        <v>73</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>341</v>
+        <v>73</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>73</v>
@@ -6626,13 +6389,13 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>93</v>
@@ -6641,7 +6404,7 @@
         <v>94</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>73</v>
@@ -6649,10 +6412,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6663,7 +6426,7 @@
         <v>74</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>73</v>
@@ -6675,15 +6438,17 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>73</v>
@@ -6732,7 +6497,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6747,7 +6512,7 @@
         <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>101</v>
+        <v>343</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
@@ -6755,10 +6520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6861,10 +6626,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6969,14 +6734,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>350</v>
+        <v>299</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6998,10 +6763,10 @@
         <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
+        <v>300</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>352</v>
+        <v>301</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>107</v>
@@ -7056,7 +6821,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -7079,10 +6844,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7093,7 +6858,7 @@
         <v>74</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>73</v>
@@ -7105,16 +6870,16 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7140,13 +6905,13 @@
         <v>73</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>141</v>
+        <v>235</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>73</v>
@@ -7164,13 +6929,13 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>93</v>
@@ -7179,7 +6944,7 @@
         <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>73</v>
@@ -7187,10 +6952,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7213,13 +6978,13 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>98</v>
+        <v>353</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>99</v>
+        <v>354</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7270,7 +7035,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>100</v>
+        <v>352</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -7279,13 +7044,13 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>101</v>
+        <v>343</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
@@ -7293,21 +7058,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>73</v>
@@ -7319,16 +7084,16 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>104</v>
+        <v>356</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>105</v>
+        <v>357</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>106</v>
+        <v>358</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>107</v>
+        <v>359</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7366,34 +7131,34 @@
         <v>73</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>111</v>
+        <v>355</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>95</v>
+        <v>343</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>73</v>
@@ -7401,10 +7166,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7415,7 +7180,7 @@
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>73</v>
@@ -7424,23 +7189,21 @@
         <v>73</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>137</v>
+        <v>356</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>242</v>
+        <v>361</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>243</v>
+        <v>362</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>73</v>
       </c>
@@ -7488,13 +7251,13 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>246</v>
+        <v>360</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>93</v>
@@ -7503,7 +7266,7 @@
         <v>94</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>247</v>
+        <v>343</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>73</v>
@@ -7511,10 +7274,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7525,7 +7288,7 @@
         <v>74</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>73</v>
@@ -7537,13 +7300,13 @@
         <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>97</v>
+        <v>293</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>98</v>
+        <v>364</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>99</v>
+        <v>365</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7594,22 +7357,22 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>100</v>
+        <v>363</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>101</v>
+        <v>343</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>73</v>
@@ -7617,21 +7380,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>73</v>
@@ -7643,17 +7406,15 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>73</v>
@@ -7690,34 +7451,34 @@
         <v>73</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>73</v>
@@ -7725,21 +7486,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>73</v>
@@ -7748,29 +7509,27 @@
         <v>73</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>251</v>
+        <v>105</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>252</v>
+        <v>106</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>365</v>
+        <v>73</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>73</v>
@@ -7800,34 +7559,34 @@
         <v>73</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>257</v>
+        <v>95</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>73</v>
@@ -7835,44 +7594,46 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>73</v>
+        <v>299</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>73</v>
       </c>
@@ -7920,22 +7681,22 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>263</v>
+        <v>95</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>73</v>
@@ -7943,10 +7704,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7954,7 +7715,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>81</v>
@@ -7966,23 +7727,21 @@
         <v>73</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>160</v>
+        <v>97</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>265</v>
+        <v>370</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>266</v>
+        <v>371</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>73</v>
       </c>
@@ -8030,10 +7789,10 @@
         <v>73</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>269</v>
+        <v>369</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>81</v>
@@ -8045,7 +7804,7 @@
         <v>94</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>270</v>
+        <v>101</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>73</v>
@@ -8053,10 +7812,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8076,23 +7835,21 @@
         <v>73</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>97</v>
+        <v>373</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>272</v>
+        <v>374</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>273</v>
+        <v>375</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>73</v>
       </c>
@@ -8140,7 +7897,7 @@
         <v>73</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>275</v>
+        <v>372</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
@@ -8152,10 +7909,10 @@
         <v>93</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>94</v>
+        <v>377</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>276</v>
+        <v>343</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>73</v>
@@ -8163,10 +7920,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8177,7 +7934,7 @@
         <v>74</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>73</v>
@@ -8186,23 +7943,21 @@
         <v>73</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>206</v>
+        <v>97</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>278</v>
+        <v>379</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>279</v>
+        <v>380</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>73</v>
       </c>
@@ -8250,7 +8005,7 @@
         <v>73</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>282</v>
+        <v>378</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -8265,7 +8020,7 @@
         <v>94</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>73</v>
@@ -8273,10 +8028,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8287,7 +8042,7 @@
         <v>74</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>73</v>
@@ -8296,23 +8051,21 @@
         <v>73</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>97</v>
+        <v>382</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>285</v>
+        <v>383</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>286</v>
+        <v>384</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>73</v>
       </c>
@@ -8360,3590 +8113,24 @@
         <v>73</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>289</v>
+        <v>381</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>290</v>
+        <v>385</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="P70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AL94" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:21:30+00:00</t>
+    <t>2023-04-05T16:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:24:37+00:00</t>
+    <t>2023-04-05T17:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T17:39:15+00:00</t>
+    <t>2023-04-07T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-07T12:42:40+00:00</t>
+    <t>2023-04-12T10:00:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:00:48+00:00</t>
+    <t>2023-04-12T10:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:05:52+00:00</t>
+    <t>2023-04-12T10:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:08:35+00:00</t>
+    <t>2023-04-12T14:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T14:03:54+00:00</t>
+    <t>2023-04-13T07:49:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T07:49:09+00:00</t>
+    <t>2023-04-13T08:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:12:13+00:00</t>
+    <t>2023-04-13T08:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:22:34+00:00</t>
+    <t>2023-04-13T08:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:33:21+00:00</t>
+    <t>2023-04-13T08:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$53</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="346">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:34:34+00:00</t>
+    <t>2023-04-13T08:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -308,500 +311,358 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>HealthcareService.meta.id</t>
+    <t>HealthcareService.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>HealthcareService.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>HealthcareService.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>HealthcareService.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:authorizationDate</t>
+  </si>
+  <si>
+    <t>authorizationDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationDate}
+</t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:installationDate</t>
+  </si>
+  <si>
+    <t>installationDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-implementationPeriod}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>External identifiers for this item</t>
+  </si>
+  <si>
+    <t>External identifiers for this item.</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>HealthcareService.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Whether this HealthcareService record is in active use</t>
+  </si>
+  <si>
+    <t>This flag is used to mark the record to not be used. This is not used when a center is closed for maintenance, or for holidays, the notAvailable period is to be used for this.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>HealthcareService.providedBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Référence vers la structure FINESS ET</t>
+  </si>
+  <si>
+    <t>Reference vers l'id de la ressource de la structure FINESS ET à laquelle est rattaché cet equipement social</t>
+  </si>
+  <si>
+    <t>This property is recommended to be the same as the Location's managingOrganization, and if not provided should be interpreted as such. If the Location does not have a managing Organization, then this property should be populated.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>.scopingRole.Organization</t>
+  </si>
+  <si>
+    <t>HealthcareService.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service category
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Broad category of service being performed or delivered</t>
+  </si>
+  <si>
+    <t>Identifies the broad category of service being performed or delivered.</t>
+  </si>
+  <si>
+    <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>A category of the service(s) that could be provided.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>HealthcareService.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service type
+</t>
+  </si>
+  <si>
+    <t>Type of service that may be delivered or performed</t>
+  </si>
+  <si>
+    <t>The specific type of service that may be delivered or performed.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>La discipline détermine la nature de l’activité</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J136-DisciplineEquipementSocial-RASS/FHIR/JDV-J136-DisciplineEquipementSocial-RASS</t>
+  </si>
+  <si>
+    <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
+  </si>
+  <si>
+    <t>HealthcareService.specialty</t>
+  </si>
+  <si>
+    <t>Specialties handled by the HealthcareService</t>
+  </si>
+  <si>
+    <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
+  </si>
+  <si>
+    <t>A specialty that a healthcare service may provide.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+  </si>
+  <si>
+    <t>HealthcareService.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
+  </si>
+  <si>
+    <t>Location(s) where service may be provided</t>
+  </si>
+  <si>
+    <t>The location(s) where this healthcare service may be provided.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>.location.role[classCode=SDLOC]</t>
+  </si>
+  <si>
+    <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>HealthcareService.name</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>HealthcareService.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>HealthcareService.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>HealthcareService.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>HealthcareService.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:authorizationDate</t>
-  </si>
-  <si>
-    <t>authorizationDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationDate}
-</t>
-  </si>
-  <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:installationDate</t>
-  </si>
-  <si>
-    <t>installationDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-implementationPeriod}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>External identifiers for this item</t>
-  </si>
-  <si>
-    <t>External identifiers for this item.</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>HealthcareService.active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Whether this HealthcareService record is in active use</t>
-  </si>
-  <si>
-    <t>This flag is used to mark the record to not be used. This is not used when a center is closed for maintenance, or for holidays, the notAvailable period is to be used for this.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>HealthcareService.providedBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Référence vers la structure FINESS ET</t>
-  </si>
-  <si>
-    <t>Reference vers l'id de la ressource de la structure FINESS ET à laquelle est rattaché cet equipement social</t>
-  </si>
-  <si>
-    <t>This property is recommended to be the same as the Location's managingOrganization, and if not provided should be interpreted as such. If the Location does not have a managing Organization, then this property should be populated.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>.scopingRole.Organization</t>
-  </si>
-  <si>
-    <t>HealthcareService.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">service category
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Broad category of service being performed or delivered</t>
-  </si>
-  <si>
-    <t>Identifies the broad category of service being performed or delivered.</t>
-  </si>
-  <si>
-    <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
-  </si>
-  <si>
-    <t>A category of the service(s) that could be provided.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>HealthcareService.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">service type
-</t>
-  </si>
-  <si>
-    <t>Type of service that may be delivered or performed</t>
-  </si>
-  <si>
-    <t>The specific type of service that may be delivered or performed.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>La discipline détermine la nature de l’activité</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J136-DisciplineEquipementSocial-RASS/FHIR/JDV-J136-DisciplineEquipementSocial-RASS</t>
-  </si>
-  <si>
-    <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
-  </si>
-  <si>
-    <t>HealthcareService.specialty</t>
-  </si>
-  <si>
-    <t>Specialties handled by the HealthcareService</t>
-  </si>
-  <si>
-    <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
-  </si>
-  <si>
-    <t>A specialty that a healthcare service may provide.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
-  </si>
-  <si>
-    <t>HealthcareService.location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location)
-</t>
-  </si>
-  <si>
-    <t>Location(s) where service may be provided</t>
-  </si>
-  <si>
-    <t>The location(s) where this healthcare service may be provided.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>.location.role[classCode=SDLOC]</t>
-  </si>
-  <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>HealthcareService.name</t>
-  </si>
-  <si>
     <t>Description of service as presented to a consumer while searching</t>
   </si>
   <si>
@@ -943,7 +804,22 @@
     <t>HealthcareService.eligibility.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>HealthcareService.eligibility.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>HealthcareService.eligibility.modifierExtension</t>
@@ -970,6 +846,9 @@
   </si>
   <si>
     <t>Coded value for the eligibility.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Population prise en charge par l’établissement dans le cadre de l’activité associée à la discipline</t>
@@ -1343,6 +1222,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1508,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL61"/>
+  <dimension ref="A1:AL53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.1328125" customWidth="true" bestFit="true"/>
@@ -1666,7 +1560,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
@@ -1772,7 +1666,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>80</v>
       </c>
@@ -1880,7 +1774,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>88</v>
       </c>
@@ -1986,7 +1880,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>96</v>
       </c>
@@ -2008,10 +1902,10 @@
         <v>73</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>97</v>
@@ -2022,7 +1916,9 @@
       <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>73</v>
@@ -2071,7 +1967,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -2080,35 +1976,35 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -2155,28 +2051,28 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>111</v>
@@ -2185,31 +2081,31 @@
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AL6" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" hidden="true">
+      <c r="A7" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="AK6" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL6" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2225,19 +2121,19 @@
         <v>73</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2287,7 +2183,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -2302,29 +2198,29 @@
         <v>94</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -2333,19 +2229,19 @@
         <v>73</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2395,44 +2291,44 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -2441,19 +2337,19 @@
         <v>73</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2491,47 +2387,49 @@
         <v>73</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>73</v>
       </c>
@@ -2540,29 +2438,27 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>73</v>
@@ -2611,7 +2507,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2623,23 +2519,25 @@
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>73</v>
       </c>
@@ -2648,29 +2546,27 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>73</v>
@@ -2695,13 +2591,13 @@
         <v>73</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>73</v>
@@ -2719,7 +2615,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2731,16 +2627,16 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>146</v>
       </c>
@@ -2749,26 +2645,26 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>147</v>
@@ -2777,9 +2673,11 @@
         <v>148</v>
       </c>
       <c r="N12" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>73</v>
       </c>
@@ -2803,31 +2701,31 @@
         <v>73</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2839,21 +2737,21 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2864,29 +2762,27 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>73</v>
@@ -2935,13 +2831,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>93</v>
@@ -2950,18 +2846,18 @@
         <v>94</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2978,28 +2874,30 @@
         <v>73</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q14" s="2"/>
+      <c r="Q14" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="R14" t="s" s="2">
         <v>73</v>
       </c>
@@ -3019,13 +2917,13 @@
         <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>73</v>
@@ -3043,7 +2941,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -3058,29 +2956,29 @@
         <v>94</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -3089,19 +2987,19 @@
         <v>73</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3151,7 +3049,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -3163,53 +3061,53 @@
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3235,13 +3133,13 @@
         <v>73</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -3259,7 +3157,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3268,19 +3166,19 @@
         <v>75</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>183</v>
       </c>
@@ -3289,7 +3187,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3305,19 +3203,19 @@
         <v>73</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>104</v>
+        <v>174</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3343,31 +3241,31 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>190</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3379,25 +3277,23 @@
         <v>93</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3406,27 +3302,29 @@
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>73</v>
@@ -3451,13 +3349,13 @@
         <v>73</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>73</v>
+        <v>195</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>73</v>
@@ -3475,7 +3373,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -3487,25 +3385,23 @@
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>73</v>
       </c>
@@ -3514,27 +3410,29 @@
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -3583,7 +3481,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -3595,57 +3493,55 @@
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>73</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="J20" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
       </c>
@@ -3681,45 +3577,45 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>95</v>
+        <v>209</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3730,10 +3626,10 @@
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>73</v>
@@ -3742,15 +3638,17 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3799,13 +3697,13 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>93</v>
@@ -3814,18 +3712,18 @@
         <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>204</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3839,33 +3737,31 @@
         <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q22" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
         <v>73</v>
       </c>
@@ -3909,7 +3805,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3924,18 +3820,18 @@
         <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>212</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3949,7 +3845,7 @@
         <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>73</v>
@@ -3958,16 +3854,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4017,7 +3913,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -4029,53 +3925,53 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4101,13 +3997,13 @@
         <v>73</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>227</v>
+        <v>73</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>73</v>
@@ -4125,7 +4021,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -4137,25 +4033,25 @@
         <v>93</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>94</v>
+        <v>233</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>229</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>231</v>
+        <v>73</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4165,25 +4061,25 @@
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4209,31 +4105,31 @@
         <v>73</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -4245,21 +4141,21 @@
         <v>93</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4270,28 +4166,28 @@
         <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4317,13 +4213,13 @@
         <v>73</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="Y26" t="s" s="2">
         <v>242</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -4341,7 +4237,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4356,18 +4252,18 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4378,7 +4274,7 @@
         <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -4387,20 +4283,18 @@
         <v>73</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>73</v>
@@ -4449,7 +4343,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4461,21 +4355,21 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
         <v>250</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4486,7 +4380,7 @@
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -4495,20 +4389,18 @@
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>73</v>
@@ -4557,7 +4449,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4566,35 +4458,35 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>255</v>
+        <v>102</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -4603,19 +4495,19 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>130</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>259</v>
+        <v>132</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4653,16 +4545,16 @@
         <v>73</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>256</v>
@@ -4671,61 +4563,63 @@
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>262</v>
+        <v>129</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>73</v>
       </c>
@@ -4779,27 +4673,27 @@
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>266</v>
+        <v>95</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4810,7 +4704,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -4819,19 +4713,19 @@
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>268</v>
+        <v>174</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>271</v>
+        <v>187</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4857,13 +4751,13 @@
         <v>73</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>73</v>
+        <v>266</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>73</v>
+        <v>267</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>73</v>
@@ -4881,7 +4775,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4893,21 +4787,21 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>272</v>
+        <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4918,10 +4812,10 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>73</v>
@@ -4930,16 +4824,16 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4989,33 +4883,33 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>279</v>
+        <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5026,10 +4920,10 @@
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>73</v>
@@ -5038,16 +4932,16 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>245</v>
+        <v>174</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5073,13 +4967,13 @@
         <v>73</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>73</v>
+        <v>277</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>73</v>
+        <v>278</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
@@ -5097,7 +4991,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -5109,21 +5003,21 @@
         <v>93</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5134,7 +5028,7 @@
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -5146,16 +5040,16 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5181,13 +5075,13 @@
         <v>73</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>150</v>
+        <v>265</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>73</v>
@@ -5205,7 +5099,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5220,18 +5114,18 @@
         <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5245,7 +5139,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>73</v>
@@ -5254,15 +5148,17 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>293</v>
+        <v>174</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>73</v>
@@ -5287,13 +5183,13 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>73</v>
@@ -5311,7 +5207,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5326,18 +5222,18 @@
         <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5348,10 +5244,10 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>73</v>
@@ -5360,15 +5256,17 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>97</v>
+        <v>174</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>98</v>
+        <v>292</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>73</v>
@@ -5393,13 +5291,13 @@
         <v>73</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>73</v>
+        <v>294</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>73</v>
+        <v>295</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>73</v>
@@ -5417,47 +5315,47 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>100</v>
+        <v>291</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>101</v>
+        <v>279</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>73</v>
@@ -5466,17 +5364,15 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>105</v>
+        <v>297</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>73</v>
@@ -5513,49 +5409,49 @@
         <v>73</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>111</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>95</v>
+        <v>279</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>299</v>
+        <v>73</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5565,16 +5461,16 @@
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>104</v>
+        <v>247</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>300</v>
@@ -5583,11 +5479,9 @@
         <v>301</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>73</v>
       </c>
@@ -5635,7 +5529,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5647,21 +5541,21 @@
         <v>93</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>95</v>
+        <v>303</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5684,17 +5578,15 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>304</v>
+        <v>251</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>73</v>
@@ -5719,13 +5611,13 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>306</v>
+        <v>73</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>307</v>
+        <v>73</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>73</v>
@@ -5743,7 +5635,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>303</v>
+        <v>253</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5752,35 +5644,35 @@
         <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>291</v>
+        <v>102</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -5792,16 +5684,16 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>262</v>
+        <v>129</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>309</v>
+        <v>130</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>310</v>
+        <v>255</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>311</v>
+        <v>132</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5839,79 +5731,81 @@
         <v>73</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>308</v>
+        <v>256</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>312</v>
+        <v>95</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>222</v>
+        <v>129</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>259</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>260</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>73</v>
       </c>
@@ -5935,13 +5829,13 @@
         <v>73</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>317</v>
+        <v>73</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>318</v>
+        <v>73</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>73</v>
@@ -5959,7 +5853,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>313</v>
+        <v>261</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5971,21 +5865,21 @@
         <v>93</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>319</v>
+        <v>95</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6008,16 +5902,16 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>222</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>323</v>
+        <v>208</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6043,13 +5937,13 @@
         <v>73</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>73</v>
@@ -6067,7 +5961,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6082,18 +5976,18 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6104,7 +5998,7 @@
         <v>74</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>73</v>
@@ -6116,17 +6010,15 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>222</v>
+        <v>158</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>73</v>
@@ -6151,13 +6043,13 @@
         <v>73</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>73</v>
@@ -6175,13 +6067,13 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>93</v>
@@ -6190,18 +6082,18 @@
         <v>94</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>330</v>
+        <v>303</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6212,7 +6104,7 @@
         <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>73</v>
@@ -6224,16 +6116,16 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>222</v>
+        <v>316</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>234</v>
+        <v>319</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6259,13 +6151,13 @@
         <v>73</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>334</v>
+        <v>73</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>335</v>
+        <v>73</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>73</v>
@@ -6283,13 +6175,13 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>93</v>
@@ -6298,18 +6190,18 @@
         <v>94</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6320,7 +6212,7 @@
         <v>74</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>73</v>
@@ -6332,15 +6224,17 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>206</v>
+        <v>316</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>73</v>
@@ -6389,7 +6283,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6404,18 +6298,18 @@
         <v>94</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6426,10 +6320,10 @@
         <v>74</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>73</v>
@@ -6438,17 +6332,15 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>73</v>
@@ -6497,7 +6389,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6512,18 +6404,18 @@
         <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>343</v>
+        <v>303</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6546,13 +6438,13 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>97</v>
+        <v>205</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>98</v>
+        <v>251</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>99</v>
+        <v>252</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6603,7 +6495,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>100</v>
+        <v>253</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -6618,22 +6510,22 @@
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6652,16 +6544,16 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>106</v>
+        <v>255</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6699,19 +6591,19 @@
         <v>73</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>111</v>
+        <v>256</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -6723,7 +6615,7 @@
         <v>93</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>95</v>
@@ -6732,16 +6624,16 @@
         <v>73</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6760,19 +6652,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>73</v>
@@ -6821,7 +6713,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6833,7 +6725,7 @@
         <v>93</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>95</v>
@@ -6842,12 +6734,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6855,10 +6747,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>73</v>
@@ -6870,16 +6762,16 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>254</v>
+        <v>208</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6905,13 +6797,13 @@
         <v>73</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>235</v>
+        <v>73</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>350</v>
+        <v>73</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>351</v>
+        <v>73</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>73</v>
@@ -6929,13 +6821,13 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>93</v>
@@ -6944,18 +6836,18 @@
         <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>343</v>
+        <v>102</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6978,15 +6870,17 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>206</v>
+        <v>333</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>73</v>
@@ -7035,7 +6929,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -7047,21 +6941,21 @@
         <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>94</v>
+        <v>337</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>343</v>
+        <v>303</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7075,7 +6969,7 @@
         <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>73</v>
@@ -7084,16 +6978,16 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>356</v>
+        <v>205</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>359</v>
+        <v>208</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7143,7 +7037,7 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7158,18 +7052,18 @@
         <v>94</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>343</v>
+        <v>303</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>73</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7180,10 +7074,10 @@
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>73</v>
@@ -7192,16 +7086,16 @@
         <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>359</v>
+        <v>201</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7251,890 +7145,46 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AL61" t="s" s="2">
         <v>73</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AL53">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI52">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:54:00+00:00</t>
+    <t>2023-04-13T09:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T09:51:53+00:00</t>
+    <t>2023-04-13T10:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T10:21:56+00:00</t>
+    <t>2023-04-13T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T12:58:26+00:00</t>
+    <t>2023-04-13T15:00:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:00:08+00:00</t>
+    <t>2023-04-13T15:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:16:05+00:00</t>
+    <t>2023-04-14T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:31:23+00:00</t>
+    <t>2023-04-14T12:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:45:28+00:00</t>
+    <t>2023-04-14T13:02:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:02:26+00:00</t>
+    <t>2023-04-14T13:12:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:12:31+00:00</t>
+    <t>2023-04-17T08:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:15:24+00:00</t>
+    <t>2023-04-17T08:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:17:23+00:00</t>
+    <t>2023-04-17T08:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:37:32+00:00</t>
+    <t>2023-04-17T09:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T09:07:20+00:00</t>
+    <t>2023-04-17T10:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:39:40+00:00</t>
+    <t>2023-04-17T10:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:56:20+00:00</t>
+    <t>2023-04-17T11:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:14:19+00:00</t>
+    <t>2023-04-17T11:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:17:21+00:00</t>
+    <t>2023-04-17T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:39:02+00:00</t>
+    <t>2023-04-17T11:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:54:58+00:00</t>
+    <t>2023-04-17T12:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:02:32+00:00</t>
+    <t>2023-04-17T13:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T13:37:35+00:00</t>
+    <t>2023-04-17T14:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T14:05:09+00:00</t>
+    <t>2023-04-20T17:39:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:39:34+00:00</t>
+    <t>2023-04-20T17:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="386">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,13 +311,193 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>HealthcareService.implicitRules</t>
+    <t>HealthcareService.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>HealthcareService.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>HealthcareService.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -328,9 +508,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>HealthcareService.language</t>
@@ -413,38 +590,10 @@
     <t>HealthcareService.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>HealthcareService.extension:authorizationDate</t>
@@ -576,9 +725,6 @@
     <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>A category of the service(s) that could be provided.</t>
   </si>
   <si>
@@ -659,10 +805,6 @@
     <t>HealthcareService.name</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Description of service as presented to a consumer while searching</t>
   </si>
   <si>
@@ -804,22 +946,7 @@
     <t>HealthcareService.eligibility.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>HealthcareService.eligibility.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>HealthcareService.eligibility.modifierExtension</t>
@@ -846,9 +973,6 @@
   </si>
   <si>
     <t>Coded value for the eligibility.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Population prise en charge par l’établissement dans le cadre de l’activité associée à la discipline</t>
@@ -1402,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL53"/>
+  <dimension ref="A1:AL61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.1328125" customWidth="true" bestFit="true"/>
@@ -1902,10 +2026,10 @@
         <v>73</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>97</v>
@@ -1916,9 +2040,7 @@
       <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>100</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>73</v>
@@ -1967,7 +2089,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -1976,13 +2098,13 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>73</v>
@@ -1990,21 +2112,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -2051,28 +2173,28 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AD6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>111</v>
@@ -2081,16 +2203,16 @@
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>73</v>
@@ -2098,14 +2220,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2121,19 +2243,19 @@
         <v>73</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2183,7 +2305,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -2198,7 +2320,7 @@
         <v>94</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>73</v>
@@ -2206,21 +2328,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -2229,19 +2351,19 @@
         <v>73</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2291,22 +2413,22 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>73</v>
@@ -2314,21 +2436,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -2337,19 +2459,19 @@
         <v>73</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2387,34 +2509,34 @@
         <v>73</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>73</v>
@@ -2422,14 +2544,12 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>73</v>
       </c>
@@ -2438,27 +2558,29 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>73</v>
@@ -2507,7 +2629,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2519,10 +2641,10 @@
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
@@ -2530,14 +2652,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>73</v>
       </c>
@@ -2546,27 +2666,29 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>73</v>
@@ -2591,13 +2713,13 @@
         <v>73</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>73</v>
@@ -2615,7 +2737,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2627,10 +2749,10 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>73</v>
@@ -2645,7 +2767,7 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2658,13 +2780,13 @@
         <v>73</v>
       </c>
       <c r="I12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="J12" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>147</v>
@@ -2673,11 +2795,9 @@
         <v>148</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O12" t="s" s="2">
         <v>149</v>
       </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>73</v>
       </c>
@@ -2701,31 +2821,31 @@
         <v>73</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2737,10 +2857,10 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>73</v>
@@ -2748,10 +2868,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2762,27 +2882,29 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>73</v>
@@ -2831,13 +2953,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>93</v>
@@ -2846,18 +2968,18 @@
         <v>94</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>156</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2874,30 +2996,28 @@
         <v>73</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q14" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
         <v>73</v>
       </c>
@@ -2917,13 +3037,13 @@
         <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>73</v>
@@ -2941,7 +3061,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2956,22 +3076,22 @@
         <v>94</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2987,19 +3107,19 @@
         <v>73</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3049,7 +3169,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -3061,10 +3181,10 @@
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3072,14 +3192,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3089,25 +3209,25 @@
         <v>75</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3133,13 +3253,13 @@
         <v>73</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>179</v>
+        <v>73</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -3157,7 +3277,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3166,16 +3286,16 @@
         <v>75</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>95</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>182</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -3187,7 +3307,7 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3203,19 +3323,19 @@
         <v>73</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>187</v>
+        <v>107</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3241,31 +3361,31 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>188</v>
+        <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>189</v>
+        <v>73</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>190</v>
+        <v>73</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3277,10 +3397,10 @@
         <v>93</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>73</v>
@@ -3288,12 +3408,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3302,7 +3424,7 @@
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -3311,20 +3433,18 @@
         <v>73</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>73</v>
@@ -3349,13 +3469,13 @@
         <v>73</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>73</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>196</v>
+        <v>73</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>73</v>
@@ -3373,7 +3493,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -3385,10 +3505,10 @@
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>73</v>
@@ -3396,12 +3516,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>73</v>
       </c>
@@ -3410,7 +3532,7 @@
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -3419,20 +3541,18 @@
         <v>73</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -3481,7 +3601,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -3493,55 +3613,57 @@
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>202</v>
+        <v>95</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>203</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>73</v>
       </c>
@@ -3577,34 +3699,34 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>209</v>
+        <v>95</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>73</v>
@@ -3612,10 +3734,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3626,7 +3748,7 @@
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -3638,17 +3760,15 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>213</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3697,13 +3817,13 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>93</v>
@@ -3712,18 +3832,18 @@
         <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>73</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3737,31 +3857,33 @@
         <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I22" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J22" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q22" s="2"/>
+      <c r="Q22" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="R22" t="s" s="2">
         <v>73</v>
       </c>
@@ -3805,7 +3927,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3820,18 +3942,18 @@
         <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>73</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3845,7 +3967,7 @@
         <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>73</v>
@@ -3854,16 +3976,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3913,7 +4035,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3925,10 +4047,10 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>73</v>
@@ -3936,14 +4058,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>73</v>
+        <v>221</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3959,19 +4081,19 @@
         <v>73</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3997,13 +4119,13 @@
         <v>73</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>73</v>
+        <v>226</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>73</v>
+        <v>227</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>73</v>
@@ -4021,7 +4143,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -4033,25 +4155,25 @@
         <v>93</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>233</v>
+        <v>94</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>73</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>73</v>
+        <v>231</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4061,25 +4183,25 @@
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4105,13 +4227,13 @@
         <v>73</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>73</v>
+        <v>235</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>73</v>
+        <v>236</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>73</v>
+        <v>237</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -4129,7 +4251,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -4141,10 +4263,10 @@
         <v>93</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>73</v>
@@ -4152,10 +4274,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4175,19 +4297,19 @@
         <v>73</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="N26" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4213,13 +4335,13 @@
         <v>73</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="Y26" t="s" s="2">
         <v>242</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -4237,7 +4359,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4252,7 +4374,7 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>73</v>
@@ -4260,10 +4382,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4277,24 +4399,26 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>73</v>
@@ -4343,7 +4467,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4355,21 +4479,21 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>102</v>
+        <v>249</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>73</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4383,24 +4507,26 @@
         <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>205</v>
+        <v>97</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>73</v>
@@ -4449,7 +4575,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4458,13 +4584,13 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>102</v>
+        <v>255</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>73</v>
@@ -4472,42 +4598,42 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>130</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>132</v>
+        <v>259</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4545,16 +4671,16 @@
         <v>73</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>256</v>
@@ -4563,16 +4689,16 @@
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -4580,46 +4706,44 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>258</v>
+        <v>73</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>129</v>
+        <v>262</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>73</v>
       </c>
@@ -4673,16 +4797,16 @@
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>95</v>
+        <v>266</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
@@ -4690,10 +4814,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4707,25 +4831,25 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>187</v>
+        <v>271</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4751,31 +4875,31 @@
         <v>73</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>266</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4787,10 +4911,10 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>94</v>
+        <v>272</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>73</v>
@@ -4798,10 +4922,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4812,7 +4936,7 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -4824,16 +4948,16 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4883,22 +5007,22 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>94</v>
+        <v>279</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
@@ -4906,10 +5030,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4932,16 +5056,16 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4967,13 +5091,13 @@
         <v>73</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>277</v>
+        <v>73</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>278</v>
+        <v>73</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
@@ -4991,7 +5115,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -5003,10 +5127,10 @@
         <v>93</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
@@ -5014,10 +5138,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5031,7 +5155,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>73</v>
@@ -5040,16 +5164,16 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5075,13 +5199,13 @@
         <v>73</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>265</v>
+        <v>150</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>73</v>
@@ -5099,7 +5223,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5114,7 +5238,7 @@
         <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
@@ -5122,10 +5246,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5139,7 +5263,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>73</v>
@@ -5148,17 +5272,15 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>174</v>
+        <v>293</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>73</v>
@@ -5183,13 +5305,13 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>73</v>
@@ -5207,7 +5329,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5219,10 +5341,10 @@
         <v>93</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>290</v>
+        <v>101</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
@@ -5230,10 +5352,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5244,10 +5366,10 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>73</v>
@@ -5256,17 +5378,15 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>98</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>73</v>
@@ -5291,13 +5411,13 @@
         <v>73</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>294</v>
+        <v>73</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>295</v>
+        <v>73</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>73</v>
@@ -5315,22 +5435,22 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>291</v>
+        <v>100</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>279</v>
+        <v>101</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5338,24 +5458,24 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>73</v>
@@ -5364,15 +5484,17 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>297</v>
+        <v>105</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>73</v>
@@ -5409,34 +5531,34 @@
         <v>73</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>296</v>
+        <v>111</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>279</v>
+        <v>95</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
@@ -5444,14 +5566,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>73</v>
+        <v>299</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5461,16 +5583,16 @@
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I38" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J38" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>247</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>300</v>
@@ -5479,9 +5601,11 @@
         <v>301</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>73</v>
       </c>
@@ -5529,7 +5653,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5541,10 +5665,10 @@
         <v>93</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>303</v>
+        <v>95</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
@@ -5552,10 +5676,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5578,15 +5702,17 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>251</v>
+        <v>304</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>73</v>
@@ -5611,13 +5737,13 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>73</v>
+        <v>306</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>73</v>
+        <v>307</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>73</v>
@@ -5635,7 +5761,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>253</v>
+        <v>303</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5644,13 +5770,13 @@
         <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>102</v>
+        <v>291</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>73</v>
@@ -5658,24 +5784,24 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>73</v>
@@ -5684,16 +5810,16 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>129</v>
+        <v>262</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>130</v>
+        <v>309</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>255</v>
+        <v>310</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5731,34 +5857,34 @@
         <v>73</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>95</v>
+        <v>312</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -5766,14 +5892,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>258</v>
+        <v>73</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5783,29 +5909,27 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>129</v>
+        <v>222</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>259</v>
+        <v>314</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>260</v>
+        <v>315</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>73</v>
       </c>
@@ -5829,13 +5953,13 @@
         <v>73</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>73</v>
+        <v>317</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>73</v>
+        <v>318</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>73</v>
@@ -5853,7 +5977,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>261</v>
+        <v>313</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5865,10 +5989,10 @@
         <v>93</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>73</v>
@@ -5876,10 +6000,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5902,16 +6026,16 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>104</v>
+        <v>222</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>208</v>
+        <v>323</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5937,13 +6061,13 @@
         <v>73</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>73</v>
@@ -5961,7 +6085,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5976,7 +6100,7 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
@@ -5984,10 +6108,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5998,10 +6122,10 @@
         <v>74</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>73</v>
@@ -6010,15 +6134,17 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>73</v>
@@ -6043,13 +6169,13 @@
         <v>73</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>73</v>
@@ -6067,13 +6193,13 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>93</v>
@@ -6082,7 +6208,7 @@
         <v>94</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>303</v>
+        <v>330</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>73</v>
@@ -6090,10 +6216,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6104,10 +6230,10 @@
         <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>73</v>
@@ -6116,16 +6242,16 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>316</v>
+        <v>222</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>319</v>
+        <v>234</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6151,13 +6277,13 @@
         <v>73</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>73</v>
+        <v>334</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>73</v>
+        <v>335</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>73</v>
@@ -6175,13 +6301,13 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>93</v>
@@ -6190,7 +6316,7 @@
         <v>94</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>73</v>
@@ -6198,10 +6324,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6215,7 +6341,7 @@
         <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>73</v>
@@ -6224,17 +6350,15 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>316</v>
+        <v>206</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>73</v>
@@ -6283,7 +6407,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6298,7 +6422,7 @@
         <v>94</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>73</v>
@@ -6306,10 +6430,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6332,15 +6456,17 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>73</v>
@@ -6389,7 +6515,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6404,7 +6530,7 @@
         <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
@@ -6412,10 +6538,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6438,13 +6564,13 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>205</v>
+        <v>97</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>251</v>
+        <v>98</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>252</v>
+        <v>99</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6495,7 +6621,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -6510,7 +6636,7 @@
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
@@ -6518,14 +6644,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6544,16 +6670,16 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>255</v>
+        <v>106</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6591,19 +6717,19 @@
         <v>73</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -6615,7 +6741,7 @@
         <v>93</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>95</v>
@@ -6626,14 +6752,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6652,19 +6778,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>73</v>
@@ -6713,7 +6839,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6725,7 +6851,7 @@
         <v>93</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>95</v>
@@ -6736,10 +6862,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6747,10 +6873,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>73</v>
@@ -6762,16 +6888,16 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6797,13 +6923,13 @@
         <v>73</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>73</v>
+        <v>235</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>73</v>
+        <v>350</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>73</v>
+        <v>351</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>73</v>
@@ -6821,13 +6947,13 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>93</v>
@@ -6836,7 +6962,7 @@
         <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>102</v>
+        <v>343</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>73</v>
@@ -6844,10 +6970,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6870,17 +6996,15 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>333</v>
+        <v>206</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>73</v>
@@ -6929,7 +7053,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -6941,10 +7065,10 @@
         <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>337</v>
+        <v>94</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
@@ -6952,10 +7076,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6969,7 +7093,7 @@
         <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>73</v>
@@ -6978,16 +7102,16 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>205</v>
+        <v>356</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>208</v>
+        <v>359</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7037,7 +7161,7 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7052,7 +7176,7 @@
         <v>94</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>73</v>
@@ -7060,10 +7184,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7074,10 +7198,10 @@
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>73</v>
@@ -7086,16 +7210,16 @@
         <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>201</v>
+        <v>359</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7145,29 +7269,891 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL53">
+  <autoFilter ref="A1:AL61">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7177,7 +8163,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI52">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:09:12+00:00</t>
+    <t>2023-04-28T15:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:34:44+00:00</t>
+    <t>2023-05-02T07:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$53</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="347">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T07:22:02+00:00</t>
+    <t>2023-05-02T14:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,500 +311,361 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>HealthcareService.meta.id</t>
+    <t>HealthcareService.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>HealthcareService.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>HealthcareService.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>HealthcareService.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:authorizationDate</t>
+  </si>
+  <si>
+    <t>authorizationDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationDate}
+</t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:installationDate</t>
+  </si>
+  <si>
+    <t>installationDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-implementationPeriod}
+</t>
+  </si>
+  <si>
+    <t>HealthcareService.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>numeroAutorisationARHGOS</t>
+  </si>
+  <si>
+    <t>External identifiers for this item.</t>
+  </si>
+  <si>
+    <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>HealthcareService.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Whether this HealthcareService record is in active use</t>
+  </si>
+  <si>
+    <t>This flag is used to mark the record to not be used. This is not used when a center is closed for maintenance, or for holidays, the notAvailable period is to be used for this.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>HealthcareService.providedBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-organization)
+</t>
+  </si>
+  <si>
+    <t>idStructure</t>
+  </si>
+  <si>
+    <t>The organization that provides this healthcare service.</t>
+  </si>
+  <si>
+    <t>Reference vers l'id de la ressource de la structure FINESS ET à laquelle est rattaché cet equipement social</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>.scopingRole.Organization</t>
+  </si>
+  <si>
+    <t>HealthcareService.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service category
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>disciplineEquipementSociale</t>
+  </si>
+  <si>
+    <t>Identifies the broad category of service being performed or delivered.</t>
+  </si>
+  <si>
+    <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>A category of the service(s) that could be provided.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>HealthcareService.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service type
+</t>
+  </si>
+  <si>
+    <t>Type of service that may be delivered or performed</t>
+  </si>
+  <si>
+    <t>The specific type of service that may be delivered or performed.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>La discipline détermine la nature de l’activité</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J136-DisciplineEquipementSocial-RASS/FHIR/JDV-J136-DisciplineEquipementSocial-RASS</t>
+  </si>
+  <si>
+    <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
+  </si>
+  <si>
+    <t>HealthcareService.specialty</t>
+  </si>
+  <si>
+    <t>Specialties handled by the HealthcareService</t>
+  </si>
+  <si>
+    <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
+  </si>
+  <si>
+    <t>A specialty that a healthcare service may provide.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+  </si>
+  <si>
+    <t>HealthcareService.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
+  </si>
+  <si>
+    <t>Location(s) where service may be provided</t>
+  </si>
+  <si>
+    <t>The location(s) where this healthcare service may be provided.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>.location.role[classCode=SDLOC]</t>
+  </si>
+  <si>
+    <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>HealthcareService.name</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>HealthcareService.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>HealthcareService.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>HealthcareService.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>HealthcareService.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>HealthcareService.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:authorizationDate</t>
-  </si>
-  <si>
-    <t>authorizationDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationDate}
-</t>
-  </si>
-  <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:installationDate</t>
-  </si>
-  <si>
-    <t>installationDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-implementationPeriod}
-</t>
-  </si>
-  <si>
-    <t>HealthcareService.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>HealthcareService.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>External identifiers for this item</t>
-  </si>
-  <si>
-    <t>External identifiers for this item.</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>HealthcareService.active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Whether this HealthcareService record is in active use</t>
-  </si>
-  <si>
-    <t>This flag is used to mark the record to not be used. This is not used when a center is closed for maintenance, or for holidays, the notAvailable period is to be used for this.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>HealthcareService.providedBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Référence vers la structure FINESS ET</t>
-  </si>
-  <si>
-    <t>Reference vers l'id de la ressource de la structure FINESS ET à laquelle est rattaché cet equipement social</t>
-  </si>
-  <si>
-    <t>This property is recommended to be the same as the Location's managingOrganization, and if not provided should be interpreted as such. If the Location does not have a managing Organization, then this property should be populated.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>.scopingRole.Organization</t>
-  </si>
-  <si>
-    <t>HealthcareService.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">service category
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Broad category of service being performed or delivered</t>
-  </si>
-  <si>
-    <t>Identifies the broad category of service being performed or delivered.</t>
-  </si>
-  <si>
-    <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
-  </si>
-  <si>
-    <t>A category of the service(s) that could be provided.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>HealthcareService.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">service type
-</t>
-  </si>
-  <si>
-    <t>Type of service that may be delivered or performed</t>
-  </si>
-  <si>
-    <t>The specific type of service that may be delivered or performed.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>La discipline détermine la nature de l’activité</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J136-DisciplineEquipementSocial-RASS/FHIR/JDV-J136-DisciplineEquipementSocial-RASS</t>
-  </si>
-  <si>
-    <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
-  </si>
-  <si>
-    <t>HealthcareService.specialty</t>
-  </si>
-  <si>
-    <t>Specialties handled by the HealthcareService</t>
-  </si>
-  <si>
-    <t>Collection of specialties handled by the service site. This is more of a medical term.</t>
-  </si>
-  <si>
-    <t>A specialty that a healthcare service may provide.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
-  </si>
-  <si>
-    <t>HealthcareService.location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location)
-</t>
-  </si>
-  <si>
-    <t>Location(s) where service may be provided</t>
-  </si>
-  <si>
-    <t>The location(s) where this healthcare service may be provided.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>.location.role[classCode=SDLOC]</t>
-  </si>
-  <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>HealthcareService.name</t>
-  </si>
-  <si>
     <t>Description of service as presented to a consumer while searching</t>
   </si>
   <si>
@@ -937,7 +798,7 @@
 </t>
   </si>
   <si>
-    <t>Specific eligibility requirements required to use the service</t>
+    <t>clientele</t>
   </si>
   <si>
     <t>Does this service have specific eligibility requirements that need to be met in order to use the service?</t>
@@ -946,7 +807,22 @@
     <t>HealthcareService.eligibility.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>HealthcareService.eligibility.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>HealthcareService.eligibility.modifierExtension</t>
@@ -975,6 +851,9 @@
     <t>Coded value for the eligibility.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Population prise en charge par l’établissement dans le cadre de l’activité associée à la discipline</t>
   </si>
   <si>
@@ -1020,7 +899,7 @@
     <t>HealthcareService.characteristic</t>
   </si>
   <si>
-    <t>Collection of characteristics (attributes)</t>
+    <t>modeFonctionnement</t>
   </si>
   <si>
     <t>Collection of characteristics (attributes).</t>
@@ -1526,7 +1405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL61"/>
+  <dimension ref="A1:AL53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.1328125" customWidth="true" bestFit="true"/>
@@ -1539,7 +1418,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="114.06640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="159.0546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2026,10 +1905,10 @@
         <v>73</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>97</v>
@@ -2040,7 +1919,9 @@
       <c r="M5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>73</v>
@@ -2089,7 +1970,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -2098,13 +1979,13 @@
         <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>73</v>
@@ -2112,21 +1993,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -2173,28 +2054,28 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>111</v>
@@ -2203,16 +2084,16 @@
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>73</v>
@@ -2220,14 +2101,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2243,19 +2124,19 @@
         <v>73</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2305,7 +2186,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -2320,7 +2201,7 @@
         <v>94</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>73</v>
@@ -2328,21 +2209,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -2351,19 +2232,19 @@
         <v>73</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2413,22 +2294,22 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>73</v>
@@ -2436,21 +2317,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -2459,19 +2340,19 @@
         <v>73</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2509,34 +2390,34 @@
         <v>73</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>73</v>
@@ -2544,12 +2425,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>73</v>
       </c>
@@ -2558,29 +2441,27 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>73</v>
@@ -2629,7 +2510,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2641,10 +2522,10 @@
         <v>93</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
@@ -2652,12 +2533,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>73</v>
       </c>
@@ -2666,29 +2549,27 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>73</v>
@@ -2713,13 +2594,13 @@
         <v>73</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>73</v>
@@ -2737,7 +2618,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2749,10 +2630,10 @@
         <v>93</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>73</v>
@@ -2767,7 +2648,7 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2780,13 +2661,13 @@
         <v>73</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>147</v>
@@ -2795,9 +2676,11 @@
         <v>148</v>
       </c>
       <c r="N12" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>73</v>
       </c>
@@ -2821,31 +2704,31 @@
         <v>73</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2857,10 +2740,10 @@
         <v>93</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>73</v>
@@ -2868,10 +2751,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2882,28 +2765,28 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2953,13 +2836,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>93</v>
@@ -2968,18 +2851,18 @@
         <v>94</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2996,28 +2879,30 @@
         <v>73</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q14" s="2"/>
+      <c r="Q14" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="R14" t="s" s="2">
         <v>73</v>
       </c>
@@ -3037,13 +2922,13 @@
         <v>73</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>73</v>
@@ -3061,7 +2946,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -3076,22 +2961,22 @@
         <v>94</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3107,19 +2992,19 @@
         <v>73</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3169,7 +3054,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -3181,10 +3066,10 @@
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>94</v>
+        <v>171</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3192,14 +3077,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3209,25 +3094,25 @@
         <v>75</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3253,13 +3138,13 @@
         <v>73</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>73</v>
+        <v>181</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -3277,7 +3162,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3286,28 +3171,28 @@
         <v>75</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>73</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3323,19 +3208,19 @@
         <v>73</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>104</v>
+        <v>175</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>107</v>
+        <v>188</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3361,31 +3246,31 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>190</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3397,10 +3282,10 @@
         <v>93</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>73</v>
@@ -3408,14 +3293,12 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>73</v>
       </c>
@@ -3424,27 +3307,29 @@
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K18" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>73</v>
@@ -3469,13 +3354,13 @@
         <v>73</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>73</v>
@@ -3493,7 +3378,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -3505,10 +3390,10 @@
         <v>93</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>95</v>
+        <v>192</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>73</v>
@@ -3516,14 +3401,12 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>73</v>
       </c>
@@ -3532,27 +3415,29 @@
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -3601,7 +3486,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -3613,57 +3498,55 @@
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>73</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="J20" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
       </c>
@@ -3699,34 +3582,34 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>73</v>
@@ -3734,10 +3617,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3748,10 +3631,10 @@
         <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>73</v>
@@ -3760,15 +3643,17 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3817,13 +3702,13 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>93</v>
@@ -3832,18 +3717,18 @@
         <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>204</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3860,30 +3745,28 @@
         <v>73</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="Q22" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
         <v>73</v>
       </c>
@@ -3927,7 +3810,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3942,18 +3825,18 @@
         <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>212</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3976,16 +3859,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4035,7 +3918,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -4047,10 +3930,10 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>73</v>
@@ -4058,14 +3941,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>221</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4075,25 +3958,25 @@
         <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4119,13 +4002,13 @@
         <v>73</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>227</v>
+        <v>73</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>73</v>
@@ -4143,7 +4026,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -4155,25 +4038,25 @@
         <v>93</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>94</v>
+        <v>234</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>229</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>231</v>
+        <v>73</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4189,19 +4072,19 @@
         <v>73</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4227,31 +4110,31 @@
         <v>73</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>235</v>
+        <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -4263,10 +4146,10 @@
         <v>93</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>94</v>
+        <v>171</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>73</v>
@@ -4274,10 +4157,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4291,25 +4174,25 @@
         <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4335,13 +4218,13 @@
         <v>73</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -4359,7 +4242,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4374,7 +4257,7 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>73</v>
@@ -4382,10 +4265,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4405,20 +4288,18 @@
         <v>73</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>73</v>
@@ -4467,7 +4348,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4479,13 +4360,13 @@
         <v>93</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>250</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -4507,16 +4388,16 @@
         <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>252</v>
@@ -4524,9 +4405,7 @@
       <c r="M28" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N28" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>73</v>
@@ -4575,7 +4454,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4584,13 +4463,13 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>255</v>
+        <v>102</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>73</v>
@@ -4598,42 +4477,42 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>257</v>
+        <v>130</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>259</v>
+        <v>132</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4671,34 +4550,34 @@
         <v>73</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>95</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -4706,44 +4585,46 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I30" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J30" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>262</v>
+        <v>129</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>73</v>
       </c>
@@ -4791,22 +4672,22 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>266</v>
+        <v>95</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>73</v>
@@ -4814,10 +4695,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4831,25 +4712,25 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>268</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>271</v>
+        <v>188</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4875,13 +4756,13 @@
         <v>73</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>73</v>
+        <v>266</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>73</v>
+        <v>267</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>73</v>
+        <v>268</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>73</v>
@@ -4899,7 +4780,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4911,10 +4792,10 @@
         <v>93</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>272</v>
+        <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>73</v>
@@ -4922,10 +4803,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4936,10 +4817,10 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>73</v>
@@ -4948,16 +4829,16 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5007,22 +4888,22 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>279</v>
+        <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
@@ -5030,10 +4911,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5047,7 +4928,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>73</v>
@@ -5056,16 +4937,16 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5091,13 +4972,13 @@
         <v>73</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>73</v>
+        <v>278</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>73</v>
+        <v>279</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
@@ -5115,7 +4996,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -5127,10 +5008,10 @@
         <v>93</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>218</v>
+        <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
@@ -5138,10 +5019,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5164,16 +5045,16 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5199,13 +5080,13 @@
         <v>73</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>150</v>
+        <v>266</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>73</v>
@@ -5223,7 +5104,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5238,7 +5119,7 @@
         <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
@@ -5246,10 +5127,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5272,15 +5153,17 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>293</v>
+        <v>175</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>73</v>
@@ -5305,13 +5188,13 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>73</v>
@@ -5329,7 +5212,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5341,10 +5224,10 @@
         <v>93</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>101</v>
+        <v>291</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
@@ -5352,10 +5235,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5366,7 +5249,7 @@
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
@@ -5378,15 +5261,17 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>98</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>73</v>
@@ -5411,13 +5296,13 @@
         <v>73</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>73</v>
+        <v>295</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>73</v>
+        <v>296</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>73</v>
@@ -5435,22 +5320,22 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>100</v>
+        <v>292</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>101</v>
+        <v>280</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5465,14 +5350,14 @@
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>73</v>
@@ -5484,17 +5369,15 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>104</v>
+        <v>159</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>105</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>73</v>
@@ -5531,34 +5414,34 @@
         <v>73</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>111</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>95</v>
+        <v>280</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
@@ -5566,14 +5449,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>299</v>
+        <v>73</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5586,26 +5469,24 @@
         <v>73</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>104</v>
+        <v>248</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>73</v>
       </c>
@@ -5653,7 +5534,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5665,10 +5546,10 @@
         <v>93</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>95</v>
+        <v>304</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
@@ -5676,10 +5557,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5702,17 +5583,15 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>73</v>
@@ -5737,13 +5616,13 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>306</v>
+        <v>73</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>307</v>
+        <v>73</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>73</v>
@@ -5761,7 +5640,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>303</v>
+        <v>254</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5770,13 +5649,13 @@
         <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>291</v>
+        <v>102</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>73</v>
@@ -5784,24 +5663,24 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>73</v>
@@ -5810,16 +5689,16 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>262</v>
+        <v>129</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>309</v>
+        <v>130</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>310</v>
+        <v>256</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>311</v>
+        <v>132</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5857,34 +5736,34 @@
         <v>73</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>308</v>
+        <v>257</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>312</v>
+        <v>95</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -5892,14 +5771,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5909,27 +5788,29 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="I41" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="J41" t="s" s="2">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>222</v>
+        <v>129</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>73</v>
       </c>
@@ -5953,13 +5834,13 @@
         <v>73</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>317</v>
+        <v>73</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>318</v>
+        <v>73</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>73</v>
@@ -5977,7 +5858,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>313</v>
+        <v>262</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5989,10 +5870,10 @@
         <v>93</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>319</v>
+        <v>95</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>73</v>
@@ -6000,10 +5881,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6026,16 +5907,16 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>222</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>323</v>
+        <v>209</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6061,13 +5942,13 @@
         <v>73</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>141</v>
+        <v>189</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>73</v>
@@ -6085,7 +5966,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6100,7 +5981,7 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
@@ -6108,10 +5989,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6122,10 +6003,10 @@
         <v>74</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>73</v>
@@ -6134,17 +6015,15 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>73</v>
@@ -6169,13 +6048,13 @@
         <v>73</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>73</v>
@@ -6193,13 +6072,13 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>93</v>
@@ -6208,7 +6087,7 @@
         <v>94</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>73</v>
@@ -6216,10 +6095,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6230,10 +6109,10 @@
         <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>73</v>
@@ -6242,16 +6121,16 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>222</v>
+        <v>317</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6277,13 +6156,13 @@
         <v>73</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>334</v>
+        <v>73</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>335</v>
+        <v>73</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>73</v>
@@ -6301,13 +6180,13 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>93</v>
@@ -6316,7 +6195,7 @@
         <v>94</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>73</v>
@@ -6324,10 +6203,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6341,7 +6220,7 @@
         <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>73</v>
@@ -6350,15 +6229,17 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>206</v>
+        <v>317</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>73</v>
@@ -6407,7 +6288,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6422,7 +6303,7 @@
         <v>94</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>73</v>
@@ -6430,10 +6311,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6447,7 +6328,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>73</v>
@@ -6456,17 +6337,15 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>293</v>
+        <v>248</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>73</v>
@@ -6515,7 +6394,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6530,7 +6409,7 @@
         <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>343</v>
+        <v>304</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
@@ -6538,10 +6417,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6564,13 +6443,13 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>98</v>
+        <v>252</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>99</v>
+        <v>253</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6621,7 +6500,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>100</v>
+        <v>254</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -6636,7 +6515,7 @@
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
@@ -6644,14 +6523,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6670,16 +6549,16 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>106</v>
+        <v>256</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6717,19 +6596,19 @@
         <v>73</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>111</v>
+        <v>257</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -6741,7 +6620,7 @@
         <v>93</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>95</v>
@@ -6752,14 +6631,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>299</v>
+        <v>259</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6778,19 +6657,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>73</v>
@@ -6839,7 +6718,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6851,7 +6730,7 @@
         <v>93</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>95</v>
@@ -6862,10 +6741,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6873,10 +6752,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>73</v>
@@ -6888,16 +6767,16 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6923,13 +6802,13 @@
         <v>73</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>235</v>
+        <v>73</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>350</v>
+        <v>73</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>351</v>
+        <v>73</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>73</v>
@@ -6947,13 +6826,13 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>93</v>
@@ -6962,7 +6841,7 @@
         <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>343</v>
+        <v>102</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>73</v>
@@ -6970,10 +6849,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6996,15 +6875,17 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>206</v>
+        <v>334</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>73</v>
@@ -7053,7 +6934,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -7065,10 +6946,10 @@
         <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>94</v>
+        <v>338</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>343</v>
+        <v>304</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
@@ -7076,10 +6957,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7102,16 +6983,16 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>356</v>
+        <v>206</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>359</v>
+        <v>209</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7161,7 +7042,7 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7176,7 +7057,7 @@
         <v>94</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>343</v>
+        <v>304</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>73</v>
@@ -7184,10 +7065,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7198,7 +7079,7 @@
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>73</v>
@@ -7210,16 +7091,16 @@
         <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>359</v>
+        <v>202</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7269,891 +7150,29 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>94</v>
+        <v>171</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AL61" t="s" s="2">
         <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL61">
+  <autoFilter ref="A1:AL53">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8163,7 +7182,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI52">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:32:14+00:00</t>
+    <t>2023-05-02T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:46:32+00:00</t>
+    <t>2023-05-04T14:01:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="349">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:08:50+00:00</t>
+    <t>2023-05-05T17:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -447,30 +447,36 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>HealthcareService.extension:authorizationDate</t>
-  </si>
-  <si>
-    <t>authorizationDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-authorizationDate}
+    <t>HealthcareService.extension:as-ext-healthcareservice-authorization-date</t>
+  </si>
+  <si>
+    <t>as-ext-healthcareservice-authorization-date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-healthcareservice-authorization-date}
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:installationDate</t>
-  </si>
-  <si>
-    <t>installationDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/HealthcareService-implementationPeriod}
+    <t>Date autorisation</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la date  délivrance de l’autorisation de l’activité de soins.</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-healthcareservice-implementation-period</t>
+  </si>
+  <si>
+    <t>as-ext-healthcareservice-implementation-period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-healthcareservice-implementation-period}
 </t>
+  </si>
+  <si>
+    <t>AS HealthcareService Implementation Period Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour en compte de la date d'échéance de l'autorisation de l'activité de soins.</t>
   </si>
   <si>
     <t>HealthcareService.modifierExtension</t>
@@ -1408,9 +1414,9 @@
   <dimension ref="A1:AL53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.1328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="72.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.1328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.57421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="45.44921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2525,7 +2531,7 @@
         <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>73</v>
@@ -2564,10 +2570,10 @@
         <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2633,7 +2639,7 @@
         <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>73</v>
@@ -2641,10 +2647,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2670,16 +2676,16 @@
         <v>129</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>73</v>
@@ -2728,7 +2734,7 @@
         <v>135</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2751,10 +2757,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2777,16 +2783,16 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2836,7 +2842,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2851,18 +2857,18 @@
         <v>94</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2885,23 +2891,23 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="Q14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="R14" t="s" s="2">
         <v>73</v>
@@ -2946,7 +2952,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2961,18 +2967,18 @@
         <v>94</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2995,16 +3001,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3054,7 +3060,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -3066,10 +3072,10 @@
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3077,14 +3083,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3103,16 +3109,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3138,13 +3144,13 @@
         <v>73</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -3162,7 +3168,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -3177,22 +3183,22 @@
         <v>94</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3211,16 +3217,16 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3246,13 +3252,13 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -3270,7 +3276,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -3285,7 +3291,7 @@
         <v>94</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>73</v>
@@ -3293,10 +3299,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3319,16 +3325,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3357,10 +3363,10 @@
         <v>108</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>73</v>
@@ -3378,7 +3384,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -3393,7 +3399,7 @@
         <v>94</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>73</v>
@@ -3401,10 +3407,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3427,16 +3433,16 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3486,7 +3492,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -3498,21 +3504,21 @@
         <v>93</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3535,16 +3541,16 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3594,7 +3600,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3609,7 +3615,7 @@
         <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>73</v>
@@ -3617,10 +3623,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3643,16 +3649,16 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3702,7 +3708,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3717,7 +3723,7 @@
         <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>73</v>
@@ -3725,10 +3731,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3751,16 +3757,16 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3810,7 +3816,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3825,7 +3831,7 @@
         <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>73</v>
@@ -3833,10 +3839,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3859,16 +3865,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3918,7 +3924,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3930,10 +3936,10 @@
         <v>93</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>73</v>
@@ -3941,10 +3947,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3967,16 +3973,16 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4026,7 +4032,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -4038,10 +4044,10 @@
         <v>93</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>73</v>
@@ -4049,10 +4055,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4075,16 +4081,16 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4134,7 +4140,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -4146,10 +4152,10 @@
         <v>93</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>73</v>
@@ -4157,10 +4163,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4183,16 +4189,16 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4218,31 +4224,31 @@
         <v>73</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -4257,7 +4263,7 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>73</v>
@@ -4265,10 +4271,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4291,13 +4297,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4348,7 +4354,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -4371,10 +4377,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4397,13 +4403,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4454,7 +4460,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4477,10 +4483,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4509,7 +4515,7 @@
         <v>130</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>132</v>
@@ -4562,7 +4568,7 @@
         <v>135</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4585,14 +4591,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4614,16 +4620,16 @@
         <v>129</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>73</v>
@@ -4672,7 +4678,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4695,10 +4701,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4721,16 +4727,16 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4756,13 +4762,13 @@
         <v>73</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>73</v>
@@ -4780,7 +4786,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4795,7 +4801,7 @@
         <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>73</v>
@@ -4803,10 +4809,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4829,16 +4835,16 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4888,7 +4894,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4903,7 +4909,7 @@
         <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
@@ -4911,10 +4917,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4937,16 +4943,16 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4972,13 +4978,13 @@
         <v>73</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
@@ -4996,7 +5002,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -5011,7 +5017,7 @@
         <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>73</v>
@@ -5019,10 +5025,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5045,16 +5051,16 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5080,13 +5086,13 @@
         <v>73</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>73</v>
@@ -5104,7 +5110,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -5119,7 +5125,7 @@
         <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>73</v>
@@ -5127,10 +5133,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5153,16 +5159,16 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5212,7 +5218,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -5227,7 +5233,7 @@
         <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>73</v>
@@ -5235,10 +5241,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5261,16 +5267,16 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5296,13 +5302,13 @@
         <v>73</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>73</v>
@@ -5320,7 +5326,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -5335,7 +5341,7 @@
         <v>94</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>73</v>
@@ -5343,10 +5349,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5369,13 +5375,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5426,7 +5432,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -5441,7 +5447,7 @@
         <v>94</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>73</v>
@@ -5449,10 +5455,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5475,16 +5481,16 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5534,7 +5540,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5549,7 +5555,7 @@
         <v>94</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>73</v>
@@ -5557,10 +5563,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5583,13 +5589,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5640,7 +5646,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5663,10 +5669,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5695,7 +5701,7 @@
         <v>130</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>132</v>
@@ -5748,7 +5754,7 @@
         <v>135</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -5771,14 +5777,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5800,16 +5806,16 @@
         <v>129</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>73</v>
@@ -5858,7 +5864,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5881,10 +5887,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5910,13 +5916,13 @@
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5942,13 +5948,13 @@
         <v>73</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>73</v>
@@ -5966,7 +5972,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5981,7 +5987,7 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>73</v>
@@ -5989,10 +5995,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6015,13 +6021,13 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6072,7 +6078,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -6087,7 +6093,7 @@
         <v>94</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>73</v>
@@ -6095,10 +6101,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6121,16 +6127,16 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6180,7 +6186,7 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
@@ -6195,7 +6201,7 @@
         <v>94</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>73</v>
@@ -6203,10 +6209,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6229,16 +6235,16 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6288,7 +6294,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6303,7 +6309,7 @@
         <v>94</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>73</v>
@@ -6311,10 +6317,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6337,13 +6343,13 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6394,7 +6400,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6409,7 +6415,7 @@
         <v>94</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>73</v>
@@ -6417,10 +6423,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6443,13 +6449,13 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6500,7 +6506,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -6523,10 +6529,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6555,7 +6561,7 @@
         <v>130</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>132</v>
@@ -6608,7 +6614,7 @@
         <v>135</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -6631,14 +6637,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6660,16 +6666,16 @@
         <v>129</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>132</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>73</v>
@@ -6718,7 +6724,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6741,10 +6747,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6767,16 +6773,16 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6826,7 +6832,7 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -6849,10 +6855,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6875,16 +6881,16 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -6934,7 +6940,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -6946,10 +6952,10 @@
         <v>93</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
@@ -6957,10 +6963,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6983,16 +6989,16 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7042,7 +7048,7 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7057,7 +7063,7 @@
         <v>94</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>73</v>
@@ -7065,10 +7071,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7091,16 +7097,16 @@
         <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7150,7 +7156,7 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7162,10 +7168,10 @@
         <v>93</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>73</v>
